--- a/Excel_Day-2.xlsx
+++ b/Excel_Day-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c9fd8fd000e99bc/Desktop/10KCODERS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B23CBCA4-9BBF-49CA-B88F-9B2E88308EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B23CBCA4-9BBF-49CA-B88F-9B2E88308EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02BB715-D642-4B90-9E60-09EFEE994FF9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="205">
   <si>
@@ -652,20 +674,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="dd/mmm/yyyy"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Gill Sans MT"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Gill Sans MT"/>
       <family val="2"/>
@@ -675,17 +691,14 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Gill Sans MT"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="Gill Sans MT"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -825,60 +838,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="16">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -888,27 +901,24 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="4"/>
-        <name val="Gill Sans MT"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="thin">
+        <right/>
+        <top style="thin">
           <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -924,44 +934,25 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Gill Sans MT"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
         <top style="thin">
           <color auto="1"/>
         </top>
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -977,13 +968,13 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="dd/mmm/yyyy"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -996,8 +987,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1013,13 +1002,13 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1032,8 +1021,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1049,13 +1036,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1068,8 +1054,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1085,12 +1069,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1103,8 +1087,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1120,11 +1102,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1137,8 +1120,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1154,11 +1135,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1171,8 +1153,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1188,11 +1168,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1205,8 +1186,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1222,45 +1201,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Gill Sans MT"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Gill Sans MT"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color auto="1"/>
@@ -1271,8 +1217,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1307,23 +1251,57 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="4"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1349,21 +1327,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D6BDBB1-E5B5-40B0-BF8E-708FC31D8463}" name="Table1" displayName="Table1" ref="A1:J151" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D6BDBB1-E5B5-40B0-BF8E-708FC31D8463}" name="Table1" displayName="Table1" ref="A1:J151" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J151" xr:uid="{2D6BDBB1-E5B5-40B0-BF8E-708FC31D8463}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3AE47865-252C-4A6B-8F2D-F838FF10FE0C}" name="Product ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{D2B6165F-D2E7-45A1-8356-103CC52DA025}" name="Product Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B2B66027-4864-431A-9C67-910A62DF6DC0}" name="Category" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B48E66F6-313D-4855-9A73-01C61BEE557A}" name="Salesperson" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{477AA3CC-E121-40CE-8FFF-B23402652170}" name="Region" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B7A136B4-37C9-4B67-B1F2-1B1088E93B0A}" name="Units Sold" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{AE658888-36CE-4C48-80DA-532C947637BE}" name="Unit Price" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{68CF35A1-B2C0-4D29-9CFC-E03B9D401B3E}" name="Total Sales" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{F8A91BA6-FDD5-49C7-8F2B-9069488EE2A7}" name="Sale Date" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{5A279E22-BE2F-4175-95F2-22076B5869C7}" name="Customer Rating" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3AE47865-252C-4A6B-8F2D-F838FF10FE0C}" name="Product ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D2B6165F-D2E7-45A1-8356-103CC52DA025}" name="Product Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B2B66027-4864-431A-9C67-910A62DF6DC0}" name="Category" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{B48E66F6-313D-4855-9A73-01C61BEE557A}" name="Salesperson" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{477AA3CC-E121-40CE-8FFF-B23402652170}" name="Region" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{B7A136B4-37C9-4B67-B1F2-1B1088E93B0A}" name="Units Sold" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{AE658888-36CE-4C48-80DA-532C947637BE}" name="Unit Price" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{68CF35A1-B2C0-4D29-9CFC-E03B9D401B3E}" name="Total Sales" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{F8A91BA6-FDD5-49C7-8F2B-9069488EE2A7}" name="Sale Date" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{5A279E22-BE2F-4175-95F2-22076B5869C7}" name="Customer Rating" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1623,4862 +1601,4867 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K152"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="20.88671875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A2" s="7" t="s">
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>25</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="13">
         <v>12151</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="13">
         <v>303775</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="14">
         <v>45705</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>5</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="13">
         <v>35444</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="13">
         <v>177220</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="14">
         <v>45811</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12">
         <v>45</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="13">
         <v>50049</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="13">
         <v>2252205</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="14">
         <v>45669</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="12">
         <v>27</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="13">
         <v>44008</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="13">
         <v>1188216</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="14">
         <v>45684</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="12">
         <v>39</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="13">
         <v>58867</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="13">
         <v>2295813</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="14">
         <v>45614</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="12">
         <v>49</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="13">
         <v>41161</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="13">
         <v>2016889</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="14">
         <v>45842</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="15">
         <v>1.9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="12">
         <v>20</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="13">
         <v>22934</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="13">
         <v>458680</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="14">
         <v>45832</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="15">
         <v>1.7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="12">
         <v>13</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="13">
         <v>5042</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="13">
         <v>65546</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="14">
         <v>45708</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="15">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="12">
         <v>16</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="13">
         <v>20269</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="13">
         <v>324304</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="14">
         <v>45755</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="12">
         <v>39</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="13">
         <v>42739</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="13">
         <v>1666821</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="14">
         <v>45718</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="15">
         <v>2.4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="12">
         <v>11</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="13">
         <v>25011</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="13">
         <v>275121</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="14">
         <v>45690</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="15">
         <v>2.9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="12">
         <v>43</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="13">
         <v>79373</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="13">
         <v>3413039</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="14">
         <v>45647</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="15">
         <v>3.8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="12">
         <v>39</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="13">
         <v>79784</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="13">
         <v>3111576</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="14">
         <v>45689</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="12">
         <v>6</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="13">
         <v>5721</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="13">
         <v>34326</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="14">
         <v>45873</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="15">
         <v>3.7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="12">
         <v>7</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="13">
         <v>61842</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="13">
         <v>432894</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="14">
         <v>45753</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="15">
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="12">
         <v>28</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="13">
         <v>83072</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="13">
         <v>2326016</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="14">
         <v>45621</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="12">
         <v>12</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="13">
         <v>3734</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="13">
         <v>44808</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="14">
         <v>45706</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="12">
         <v>26</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="13">
         <v>86385</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="13">
         <v>2246010</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="14">
         <v>45774</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="12">
         <v>7</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="13">
         <v>86312</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="13">
         <v>604184</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="14">
         <v>45613</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="15">
         <v>4.3</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="12">
         <v>38</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="13">
         <v>46950</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="13">
         <v>1784100</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="14">
         <v>45864</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="15">
         <v>4.8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="12">
         <v>46</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="13">
         <v>20496</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="13">
         <v>942816</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="14">
         <v>45759</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="12">
         <v>17</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="13">
         <v>11257</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="13">
         <v>191369</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="14">
         <v>45745</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="12">
         <v>47</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="13">
         <v>84848</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="13">
         <v>3987856</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="14">
         <v>45804</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="12">
         <v>32</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="13">
         <v>72943</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="13">
         <v>2334176</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="14">
         <v>45744</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="12">
         <v>20</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="13">
         <v>7244</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="13">
         <v>144880</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="14">
         <v>45661</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="15">
         <v>1.8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="12">
         <v>26</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="13">
         <v>11166</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="13">
         <v>290316</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="14">
         <v>45881</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="12">
         <v>19</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="13">
         <v>65886</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="13">
         <v>1251834</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="14">
         <v>45890</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="12">
         <v>44</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="13">
         <v>71615</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="13">
         <v>3151060</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="14">
         <v>45675</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="12">
         <v>27</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="13">
         <v>81542</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="13">
         <v>2201634</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="14">
         <v>45842</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="12">
         <v>14</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="13">
         <v>22083</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="13">
         <v>309162</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="14">
         <v>45720</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="15">
         <v>2.9</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="12">
         <v>47</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="13">
         <v>81998</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="13">
         <v>3853906</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="14">
         <v>45778</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="12">
         <v>31</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="13">
         <v>82701</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="13">
         <v>2563731</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="14">
         <v>45903</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="12">
         <v>22</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="13">
         <v>56711</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="13">
         <v>1247642</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="14">
         <v>45624</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="12">
         <v>36</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="13">
         <v>27411</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="13">
         <v>986796</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="14">
         <v>45917</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="15">
         <v>1.9</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="12">
         <v>42</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="13">
         <v>47279</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="13">
         <v>1985718</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="14">
         <v>45752</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="15">
         <v>4.8</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="12">
         <v>9</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="13">
         <v>47181</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="13">
         <v>424629</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="14">
         <v>45644</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="15">
         <v>4.2</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="12">
         <v>10</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="13">
         <v>88669</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H38" s="13">
         <v>886690</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="14">
         <v>45745</v>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="15">
         <v>1.5</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="12">
         <v>48</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="13">
         <v>72125</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="13">
         <v>3462000</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="14">
         <v>45741</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="15">
         <v>1.5</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="12">
         <v>40</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="13">
         <v>69911</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H40" s="13">
         <v>2796440</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="14">
         <v>45851</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="12">
         <v>9</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="13">
         <v>81797</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H41" s="13">
         <v>736173</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="14">
         <v>45798</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="12">
         <v>31</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="13">
         <v>13119</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H42" s="13">
         <v>406689</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="14">
         <v>45664</v>
       </c>
-      <c r="J42" s="8">
+      <c r="J42" s="15">
         <v>3.4</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="12">
         <v>13</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="13">
         <v>10141</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="13">
         <v>131833</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="14">
         <v>45728</v>
       </c>
-      <c r="J43" s="8">
+      <c r="J43" s="15">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="12">
         <v>20</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="13">
         <v>44295</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44" s="13">
         <v>885900</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="14">
         <v>45673</v>
       </c>
-      <c r="J44" s="8">
+      <c r="J44" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="12">
         <v>21</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="13">
         <v>15036</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="13">
         <v>315756</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="14">
         <v>45803</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="15">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="12">
         <v>38</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="13">
         <v>60959</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="13">
         <v>2316442</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="14">
         <v>45744</v>
       </c>
-      <c r="J46" s="8">
+      <c r="J46" s="15">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="12">
         <v>17</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47" s="13">
         <v>76290</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H47" s="13">
         <v>1296930</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="14">
         <v>45618</v>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A48" s="7" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="12">
         <v>10</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48" s="13">
         <v>64173</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48" s="13">
         <v>641730</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="14">
         <v>45735</v>
       </c>
-      <c r="J48" s="8">
+      <c r="J48" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A49" s="7" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="12">
         <v>20</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49" s="13">
         <v>2509</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="13">
         <v>50180</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="14">
         <v>45695</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="12">
         <v>37</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="13">
         <v>78931</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H50" s="13">
         <v>2920447</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="14">
         <v>45905</v>
       </c>
-      <c r="J50" s="8">
+      <c r="J50" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="12">
         <v>48</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="13">
         <v>2170</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="13">
         <v>104160</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="14">
         <v>45925</v>
       </c>
-      <c r="J51" s="8">
+      <c r="J51" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="12">
         <v>23</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="13">
         <v>69549</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H52" s="13">
         <v>1599627</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="14">
         <v>45626</v>
       </c>
-      <c r="J52" s="8">
+      <c r="J52" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="12">
         <v>16</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53" s="13">
         <v>60484</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53" s="13">
         <v>967744</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="14">
         <v>45910</v>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A54" s="7" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="12">
         <v>31</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="13">
         <v>35226</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54" s="13">
         <v>1092006</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="14">
         <v>45815</v>
       </c>
-      <c r="J54" s="8">
+      <c r="J54" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A55" s="7" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="12">
         <v>33</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="13">
         <v>47243</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H55" s="13">
         <v>1559019</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="14">
         <v>45724</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A56" s="7" t="s">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="12">
         <v>14</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="13">
         <v>24421</v>
       </c>
-      <c r="H56" s="4">
+      <c r="H56" s="13">
         <v>341894</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="14">
         <v>45827</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="15">
         <v>3.6</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="12">
         <v>37</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="13">
         <v>18176</v>
       </c>
-      <c r="H57" s="4">
+      <c r="H57" s="13">
         <v>672512</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="14">
         <v>45919</v>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="15">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A58" s="7" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="12">
         <v>42</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="13">
         <v>3800</v>
       </c>
-      <c r="H58" s="4">
+      <c r="H58" s="13">
         <v>159600</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="14">
         <v>45768</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A59" s="7" t="s">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="12">
         <v>13</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G59" s="13">
         <v>53496</v>
       </c>
-      <c r="H59" s="4">
+      <c r="H59" s="13">
         <v>695448</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="14">
         <v>45860</v>
       </c>
-      <c r="J59" s="8">
+      <c r="J59" s="15">
         <v>2.8</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="12">
         <v>29</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G60" s="13">
         <v>67135</v>
       </c>
-      <c r="H60" s="4">
+      <c r="H60" s="13">
         <v>1946915</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="14">
         <v>45825</v>
       </c>
-      <c r="J60" s="8">
+      <c r="J60" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A61" s="7" t="s">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="12">
         <v>44</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="13">
         <v>3331</v>
       </c>
-      <c r="H61" s="4">
+      <c r="H61" s="13">
         <v>146564</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="14">
         <v>45815</v>
       </c>
-      <c r="J61" s="8">
+      <c r="J61" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A62" s="7" t="s">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="12">
         <v>31</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G62" s="13">
         <v>87246</v>
       </c>
-      <c r="H62" s="4">
+      <c r="H62" s="13">
         <v>2704626</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="14">
         <v>45828</v>
       </c>
-      <c r="J62" s="8">
+      <c r="J62" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A63" s="7" t="s">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="12">
         <v>8</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G63" s="13">
         <v>18991</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H63" s="13">
         <v>151928</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="14">
         <v>45765</v>
       </c>
-      <c r="J63" s="8">
+      <c r="J63" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A64" s="7" t="s">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="12">
         <v>35</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G64" s="13">
         <v>75938</v>
       </c>
-      <c r="H64" s="4">
+      <c r="H64" s="13">
         <v>2657830</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="14">
         <v>45772</v>
       </c>
-      <c r="J64" s="8">
+      <c r="J64" s="15">
         <v>1.7</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A65" s="7" t="s">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="12">
         <v>50</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G65" s="13">
         <v>17953</v>
       </c>
-      <c r="H65" s="4">
+      <c r="H65" s="13">
         <v>897650</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="14">
         <v>45933</v>
       </c>
-      <c r="J65" s="8">
+      <c r="J65" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A66" s="7" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="12">
         <v>33</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66" s="13">
         <v>29589</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66" s="13">
         <v>976437</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I66" s="14">
         <v>45671</v>
       </c>
-      <c r="J66" s="8">
+      <c r="J66" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A67" s="7" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="12">
         <v>28</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67" s="13">
         <v>81095</v>
       </c>
-      <c r="H67" s="4">
+      <c r="H67" s="13">
         <v>2270660</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I67" s="14">
         <v>45852</v>
       </c>
-      <c r="J67" s="8">
+      <c r="J67" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A68" s="7" t="s">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="12">
         <v>11</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68" s="13">
         <v>11682</v>
       </c>
-      <c r="H68" s="4">
+      <c r="H68" s="13">
         <v>128502</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I68" s="14">
         <v>45706</v>
       </c>
-      <c r="J68" s="8">
+      <c r="J68" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A69" s="7" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="12">
         <v>21</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69" s="13">
         <v>86277</v>
       </c>
-      <c r="H69" s="4">
+      <c r="H69" s="13">
         <v>1811817</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I69" s="14">
         <v>45711</v>
       </c>
-      <c r="J69" s="8">
+      <c r="J69" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A70" s="7" t="s">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="12">
         <v>43</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="13">
         <v>39035</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70" s="13">
         <v>1678505</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I70" s="14">
         <v>45904</v>
       </c>
-      <c r="J70" s="8">
+      <c r="J70" s="15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A71" s="7" t="s">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E71" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="12">
         <v>16</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G71" s="13">
         <v>38280</v>
       </c>
-      <c r="H71" s="4">
+      <c r="H71" s="13">
         <v>612480</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I71" s="14">
         <v>45725</v>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="15">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A72" s="7" t="s">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E72" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="12">
         <v>32</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G72" s="13">
         <v>4290</v>
       </c>
-      <c r="H72" s="4">
+      <c r="H72" s="13">
         <v>137280</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I72" s="14">
         <v>45685</v>
       </c>
-      <c r="J72" s="8">
+      <c r="J72" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A73" s="7" t="s">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E73" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="12">
         <v>9</v>
       </c>
-      <c r="G73" s="4">
+      <c r="G73" s="13">
         <v>61541</v>
       </c>
-      <c r="H73" s="4">
+      <c r="H73" s="13">
         <v>553869</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I73" s="14">
         <v>45788</v>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="15">
         <v>3.7</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A74" s="7" t="s">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E74" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="12">
         <v>19</v>
       </c>
-      <c r="G74" s="4">
+      <c r="G74" s="13">
         <v>65513</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H74" s="13">
         <v>1244747</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I74" s="14">
         <v>45860</v>
       </c>
-      <c r="J74" s="8">
+      <c r="J74" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="12">
         <v>8</v>
       </c>
-      <c r="G75" s="4">
+      <c r="G75" s="13">
         <v>29775</v>
       </c>
-      <c r="H75" s="4">
+      <c r="H75" s="13">
         <v>238200</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I75" s="14">
         <v>45820</v>
       </c>
-      <c r="J75" s="8">
+      <c r="J75" s="15">
         <v>4.8</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A76" s="7" t="s">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76" s="12">
         <v>5</v>
       </c>
-      <c r="G76" s="4">
+      <c r="G76" s="13">
         <v>79574</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H76" s="13">
         <v>397870</v>
       </c>
-      <c r="I76" s="5">
+      <c r="I76" s="14">
         <v>45802</v>
       </c>
-      <c r="J76" s="8">
+      <c r="J76" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A77" s="7" t="s">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="12">
         <v>20</v>
       </c>
-      <c r="G77" s="4">
+      <c r="G77" s="13">
         <v>61099</v>
       </c>
-      <c r="H77" s="4">
+      <c r="H77" s="13">
         <v>1221980</v>
       </c>
-      <c r="I77" s="5">
+      <c r="I77" s="14">
         <v>45636</v>
       </c>
-      <c r="J77" s="8">
+      <c r="J77" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A78" s="7" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78" s="12">
         <v>31</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="13">
         <v>64430</v>
       </c>
-      <c r="H78" s="4">
+      <c r="H78" s="13">
         <v>1997330</v>
       </c>
-      <c r="I78" s="5">
+      <c r="I78" s="14">
         <v>45914</v>
       </c>
-      <c r="J78" s="8">
+      <c r="J78" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A79" s="7" t="s">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79" s="12">
         <v>42</v>
       </c>
-      <c r="G79" s="4">
+      <c r="G79" s="13">
         <v>33388</v>
       </c>
-      <c r="H79" s="4">
+      <c r="H79" s="13">
         <v>1402296</v>
       </c>
-      <c r="I79" s="5">
+      <c r="I79" s="14">
         <v>45857</v>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="15">
         <v>4.8</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A80" s="7" t="s">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E80" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="12">
         <v>26</v>
       </c>
-      <c r="G80" s="4">
+      <c r="G80" s="13">
         <v>47323</v>
       </c>
-      <c r="H80" s="4">
+      <c r="H80" s="13">
         <v>1230398</v>
       </c>
-      <c r="I80" s="5">
+      <c r="I80" s="14">
         <v>45886</v>
       </c>
-      <c r="J80" s="8">
+      <c r="J80" s="15">
         <v>4.3</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A81" s="7" t="s">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="12">
         <v>8</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G81" s="13">
         <v>39819</v>
       </c>
-      <c r="H81" s="4">
+      <c r="H81" s="13">
         <v>318552</v>
       </c>
-      <c r="I81" s="5">
+      <c r="I81" s="14">
         <v>45925</v>
       </c>
-      <c r="J81" s="8">
+      <c r="J81" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A82" s="7" t="s">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="12">
         <v>49</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="13">
         <v>84347</v>
       </c>
-      <c r="H82" s="4">
+      <c r="H82" s="13">
         <v>4133003</v>
       </c>
-      <c r="I82" s="5">
+      <c r="I82" s="14">
         <v>45741</v>
       </c>
-      <c r="J82" s="8">
+      <c r="J82" s="15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A83" s="7" t="s">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="12">
         <v>50</v>
       </c>
-      <c r="G83" s="4">
+      <c r="G83" s="13">
         <v>73912</v>
       </c>
-      <c r="H83" s="4">
+      <c r="H83" s="13">
         <v>3695600</v>
       </c>
-      <c r="I83" s="5">
+      <c r="I83" s="14">
         <v>45928</v>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="15">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A84" s="7" t="s">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="12">
         <v>40</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="13">
         <v>51299</v>
       </c>
-      <c r="H84" s="4">
+      <c r="H84" s="13">
         <v>2051960</v>
       </c>
-      <c r="I84" s="5">
+      <c r="I84" s="14">
         <v>45960</v>
       </c>
-      <c r="J84" s="8">
+      <c r="J84" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A85" s="7" t="s">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E85" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="12">
         <v>34</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="13">
         <v>21316</v>
       </c>
-      <c r="H85" s="4">
+      <c r="H85" s="13">
         <v>724744</v>
       </c>
-      <c r="I85" s="5">
+      <c r="I85" s="14">
         <v>45731</v>
       </c>
-      <c r="J85" s="8">
+      <c r="J85" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A86" s="7" t="s">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86" s="12">
         <v>22</v>
       </c>
-      <c r="G86" s="4">
+      <c r="G86" s="13">
         <v>67123</v>
       </c>
-      <c r="H86" s="4">
+      <c r="H86" s="13">
         <v>1476706</v>
       </c>
-      <c r="I86" s="5">
+      <c r="I86" s="14">
         <v>45833</v>
       </c>
-      <c r="J86" s="8">
+      <c r="J86" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A87" s="7" t="s">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="12">
         <v>25</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="13">
         <v>76186</v>
       </c>
-      <c r="H87" s="4">
+      <c r="H87" s="13">
         <v>1904650</v>
       </c>
-      <c r="I87" s="5">
+      <c r="I87" s="14">
         <v>45658</v>
       </c>
-      <c r="J87" s="8">
+      <c r="J87" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A88" s="7" t="s">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88" s="12">
         <v>35</v>
       </c>
-      <c r="G88" s="4">
+      <c r="G88" s="13">
         <v>10707</v>
       </c>
-      <c r="H88" s="4">
+      <c r="H88" s="13">
         <v>374745</v>
       </c>
-      <c r="I88" s="5">
+      <c r="I88" s="14">
         <v>45949</v>
       </c>
-      <c r="J88" s="8">
+      <c r="J88" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A89" s="7" t="s">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="12">
         <v>26</v>
       </c>
-      <c r="G89" s="4">
+      <c r="G89" s="13">
         <v>86311</v>
       </c>
-      <c r="H89" s="4">
+      <c r="H89" s="13">
         <v>2244086</v>
       </c>
-      <c r="I89" s="5">
+      <c r="I89" s="14">
         <v>45689</v>
       </c>
-      <c r="J89" s="8">
+      <c r="J89" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A90" s="7" t="s">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E90" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="12">
         <v>9</v>
       </c>
-      <c r="G90" s="4">
+      <c r="G90" s="13">
         <v>13009</v>
       </c>
-      <c r="H90" s="4">
+      <c r="H90" s="13">
         <v>117081</v>
       </c>
-      <c r="I90" s="5">
+      <c r="I90" s="14">
         <v>45742</v>
       </c>
-      <c r="J90" s="8">
+      <c r="J90" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A91" s="7" t="s">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E91" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="12">
         <v>7</v>
       </c>
-      <c r="G91" s="4">
+      <c r="G91" s="13">
         <v>83006</v>
       </c>
-      <c r="H91" s="4">
+      <c r="H91" s="13">
         <v>581042</v>
       </c>
-      <c r="I91" s="5">
+      <c r="I91" s="14">
         <v>45638</v>
       </c>
-      <c r="J91" s="8">
+      <c r="J91" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A92" s="7" t="s">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="12">
         <v>5</v>
       </c>
-      <c r="G92" s="4">
+      <c r="G92" s="13">
         <v>60184</v>
       </c>
-      <c r="H92" s="4">
+      <c r="H92" s="13">
         <v>300920</v>
       </c>
-      <c r="I92" s="5">
+      <c r="I92" s="14">
         <v>45938</v>
       </c>
-      <c r="J92" s="8">
+      <c r="J92" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A93" s="7" t="s">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="12">
         <v>12</v>
       </c>
-      <c r="G93" s="4">
+      <c r="G93" s="13">
         <v>68917</v>
       </c>
-      <c r="H93" s="4">
+      <c r="H93" s="13">
         <v>827004</v>
       </c>
-      <c r="I93" s="5">
+      <c r="I93" s="14">
         <v>45970</v>
       </c>
-      <c r="J93" s="8">
+      <c r="J93" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A94" s="7" t="s">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="12">
         <v>31</v>
       </c>
-      <c r="G94" s="4">
+      <c r="G94" s="13">
         <v>15916</v>
       </c>
-      <c r="H94" s="4">
+      <c r="H94" s="13">
         <v>493396</v>
       </c>
-      <c r="I94" s="5">
+      <c r="I94" s="14">
         <v>45917</v>
       </c>
-      <c r="J94" s="8">
+      <c r="J94" s="15">
         <v>4.2</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A95" s="7" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="12">
         <v>25</v>
       </c>
-      <c r="G95" s="4">
+      <c r="G95" s="13">
         <v>48430</v>
       </c>
-      <c r="H95" s="4">
+      <c r="H95" s="13">
         <v>1210750</v>
       </c>
-      <c r="I95" s="5">
+      <c r="I95" s="14">
         <v>45969</v>
       </c>
-      <c r="J95" s="8">
+      <c r="J95" s="15">
         <v>1.8</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A96" s="7" t="s">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="12">
         <v>35</v>
       </c>
-      <c r="G96" s="4">
+      <c r="G96" s="13">
         <v>54863</v>
       </c>
-      <c r="H96" s="4">
+      <c r="H96" s="13">
         <v>1920205</v>
       </c>
-      <c r="I96" s="5">
+      <c r="I96" s="14">
         <v>45851</v>
       </c>
-      <c r="J96" s="8">
+      <c r="J96" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A97" s="7" t="s">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="12">
         <v>22</v>
       </c>
-      <c r="G97" s="4">
+      <c r="G97" s="13">
         <v>24224</v>
       </c>
-      <c r="H97" s="4">
+      <c r="H97" s="13">
         <v>532928</v>
       </c>
-      <c r="I97" s="5">
+      <c r="I97" s="14">
         <v>45932</v>
       </c>
-      <c r="J97" s="8">
+      <c r="J97" s="15">
         <v>1.9</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A98" s="7" t="s">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="12">
         <v>8</v>
       </c>
-      <c r="G98" s="4">
+      <c r="G98" s="13">
         <v>61083</v>
       </c>
-      <c r="H98" s="4">
+      <c r="H98" s="13">
         <v>488664</v>
       </c>
-      <c r="I98" s="5">
+      <c r="I98" s="14">
         <v>45767</v>
       </c>
-      <c r="J98" s="8">
+      <c r="J98" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A99" s="7" t="s">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="12">
         <v>31</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="13">
         <v>44325</v>
       </c>
-      <c r="H99" s="4">
+      <c r="H99" s="13">
         <v>1374075</v>
       </c>
-      <c r="I99" s="5">
+      <c r="I99" s="14">
         <v>45961</v>
       </c>
-      <c r="J99" s="8">
+      <c r="J99" s="15">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A100" s="7" t="s">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="12">
         <v>39</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="13">
         <v>23423</v>
       </c>
-      <c r="H100" s="4">
+      <c r="H100" s="13">
         <v>913497</v>
       </c>
-      <c r="I100" s="5">
+      <c r="I100" s="14">
         <v>45715</v>
       </c>
-      <c r="J100" s="8">
+      <c r="J100" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A101" s="7" t="s">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="12">
         <v>47</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="13">
         <v>43399</v>
       </c>
-      <c r="H101" s="4">
+      <c r="H101" s="13">
         <v>2039753</v>
       </c>
-      <c r="I101" s="5">
+      <c r="I101" s="14">
         <v>45787</v>
       </c>
-      <c r="J101" s="8">
+      <c r="J101" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="12">
         <v>12</v>
       </c>
-      <c r="G102" s="4">
+      <c r="G102" s="13">
         <v>88759</v>
       </c>
-      <c r="H102" s="4">
+      <c r="H102" s="13">
         <v>1065108</v>
       </c>
-      <c r="I102" s="5">
+      <c r="I102" s="14">
         <v>45636</v>
       </c>
-      <c r="J102" s="8">
+      <c r="J102" s="15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A103" s="7" t="s">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E103" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="12">
         <v>21</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="13">
         <v>20885</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="13">
         <v>438585</v>
       </c>
-      <c r="I103" s="5">
+      <c r="I103" s="14">
         <v>45750</v>
       </c>
-      <c r="J103" s="8">
+      <c r="J103" s="15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A104" s="7" t="s">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E104" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104" s="12">
         <v>5</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="13">
         <v>7259</v>
       </c>
-      <c r="H104" s="4">
+      <c r="H104" s="13">
         <v>36295</v>
       </c>
-      <c r="I104" s="5">
+      <c r="I104" s="14">
         <v>45686</v>
       </c>
-      <c r="J104" s="8">
+      <c r="J104" s="15">
         <v>3.8</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A105" s="7" t="s">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105" s="12">
         <v>42</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="13">
         <v>74681</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="13">
         <v>3136602</v>
       </c>
-      <c r="I105" s="5">
+      <c r="I105" s="14">
         <v>45939</v>
       </c>
-      <c r="J105" s="8">
+      <c r="J105" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A106" s="7" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E106" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="12">
         <v>49</v>
       </c>
-      <c r="G106" s="4">
+      <c r="G106" s="13">
         <v>68794</v>
       </c>
-      <c r="H106" s="4">
+      <c r="H106" s="13">
         <v>3370906</v>
       </c>
-      <c r="I106" s="5">
+      <c r="I106" s="14">
         <v>45684</v>
       </c>
-      <c r="J106" s="8">
+      <c r="J106" s="15">
         <v>4.8</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A107" s="7" t="s">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E107" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107" s="12">
         <v>5</v>
       </c>
-      <c r="G107" s="4">
+      <c r="G107" s="13">
         <v>61534</v>
       </c>
-      <c r="H107" s="4">
+      <c r="H107" s="13">
         <v>307670</v>
       </c>
-      <c r="I107" s="5">
+      <c r="I107" s="14">
         <v>45969</v>
       </c>
-      <c r="J107" s="8">
+      <c r="J107" s="15">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A108" s="7" t="s">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E108" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108" s="12">
         <v>27</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G108" s="13">
         <v>11345</v>
       </c>
-      <c r="H108" s="4">
+      <c r="H108" s="13">
         <v>306315</v>
       </c>
-      <c r="I108" s="5">
+      <c r="I108" s="14">
         <v>45769</v>
       </c>
-      <c r="J108" s="8">
+      <c r="J108" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A109" s="7" t="s">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="12">
         <v>20</v>
       </c>
-      <c r="G109" s="4">
+      <c r="G109" s="13">
         <v>76026</v>
       </c>
-      <c r="H109" s="4">
+      <c r="H109" s="13">
         <v>1520520</v>
       </c>
-      <c r="I109" s="5">
+      <c r="I109" s="14">
         <v>45679</v>
       </c>
-      <c r="J109" s="8">
+      <c r="J109" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A110" s="7" t="s">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="12">
         <v>35</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G110" s="13">
         <v>14412</v>
       </c>
-      <c r="H110" s="4">
+      <c r="H110" s="13">
         <v>504420</v>
       </c>
-      <c r="I110" s="5">
+      <c r="I110" s="14">
         <v>45791</v>
       </c>
-      <c r="J110" s="8">
+      <c r="J110" s="15">
         <v>3.2</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A111" s="7" t="s">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="12">
         <v>48</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="13">
         <v>33555</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H111" s="13">
         <v>1610640</v>
       </c>
-      <c r="I111" s="5">
+      <c r="I111" s="14">
         <v>45658</v>
       </c>
-      <c r="J111" s="8">
+      <c r="J111" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A112" s="7" t="s">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="12">
         <v>25</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="13">
         <v>7596</v>
       </c>
-      <c r="H112" s="4">
+      <c r="H112" s="13">
         <v>189900</v>
       </c>
-      <c r="I112" s="5">
+      <c r="I112" s="14">
         <v>45944</v>
       </c>
-      <c r="J112" s="8">
+      <c r="J112" s="15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A113" s="7" t="s">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113" s="12">
         <v>45</v>
       </c>
-      <c r="G113" s="4">
+      <c r="G113" s="13">
         <v>79114</v>
       </c>
-      <c r="H113" s="4">
+      <c r="H113" s="13">
         <v>3560130</v>
       </c>
-      <c r="I113" s="5">
+      <c r="I113" s="14">
         <v>45968</v>
       </c>
-      <c r="J113" s="8">
+      <c r="J113" s="15">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A114" s="7" t="s">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E114" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="12">
         <v>23</v>
       </c>
-      <c r="G114" s="4">
+      <c r="G114" s="13">
         <v>71009</v>
       </c>
-      <c r="H114" s="4">
+      <c r="H114" s="13">
         <v>1633207</v>
       </c>
-      <c r="I114" s="5">
+      <c r="I114" s="14">
         <v>45908</v>
       </c>
-      <c r="J114" s="8">
+      <c r="J114" s="15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A115" s="7" t="s">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="12">
         <v>42</v>
       </c>
-      <c r="G115" s="4">
+      <c r="G115" s="13">
         <v>76267</v>
       </c>
-      <c r="H115" s="4">
+      <c r="H115" s="13">
         <v>3203214</v>
       </c>
-      <c r="I115" s="5">
+      <c r="I115" s="14">
         <v>45930</v>
       </c>
-      <c r="J115" s="8">
+      <c r="J115" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A116" s="7" t="s">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="E116" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="12">
         <v>40</v>
       </c>
-      <c r="G116" s="4">
+      <c r="G116" s="13">
         <v>70009</v>
       </c>
-      <c r="H116" s="4">
+      <c r="H116" s="13">
         <v>2800360</v>
       </c>
-      <c r="I116" s="5">
+      <c r="I116" s="14">
         <v>45674</v>
       </c>
-      <c r="J116" s="8">
+      <c r="J116" s="15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A117" s="7" t="s">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E117" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="12">
         <v>21</v>
       </c>
-      <c r="G117" s="4">
+      <c r="G117" s="13">
         <v>60386</v>
       </c>
-      <c r="H117" s="4">
+      <c r="H117" s="13">
         <v>1268106</v>
       </c>
-      <c r="I117" s="5">
+      <c r="I117" s="14">
         <v>45621</v>
       </c>
-      <c r="J117" s="8">
+      <c r="J117" s="15">
         <v>4.3</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A118" s="7" t="s">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="12">
         <v>31</v>
       </c>
-      <c r="G118" s="4">
+      <c r="G118" s="13">
         <v>71517</v>
       </c>
-      <c r="H118" s="4">
+      <c r="H118" s="13">
         <v>2217027</v>
       </c>
-      <c r="I118" s="5">
+      <c r="I118" s="14">
         <v>45847</v>
       </c>
-      <c r="J118" s="8">
+      <c r="J118" s="15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A119" s="7" t="s">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="E119" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="12">
         <v>18</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="13">
         <v>46660</v>
       </c>
-      <c r="H119" s="4">
+      <c r="H119" s="13">
         <v>839880</v>
       </c>
-      <c r="I119" s="5">
+      <c r="I119" s="14">
         <v>45820</v>
       </c>
-      <c r="J119" s="8">
+      <c r="J119" s="15">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A120" s="7" t="s">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="E120" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="12">
         <v>24</v>
       </c>
-      <c r="G120" s="4">
+      <c r="G120" s="13">
         <v>81017</v>
       </c>
-      <c r="H120" s="4">
+      <c r="H120" s="13">
         <v>1944408</v>
       </c>
-      <c r="I120" s="5">
+      <c r="I120" s="14">
         <v>45946</v>
       </c>
-      <c r="J120" s="8">
+      <c r="J120" s="15">
         <v>3.2</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A121" s="7" t="s">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E121" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="12">
         <v>25</v>
       </c>
-      <c r="G121" s="4">
+      <c r="G121" s="13">
         <v>14407</v>
       </c>
-      <c r="H121" s="4">
+      <c r="H121" s="13">
         <v>360175</v>
       </c>
-      <c r="I121" s="5">
+      <c r="I121" s="14">
         <v>45714</v>
       </c>
-      <c r="J121" s="8">
+      <c r="J121" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A122" s="7" t="s">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E122" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="12">
         <v>8</v>
       </c>
-      <c r="G122" s="4">
+      <c r="G122" s="13">
         <v>79290</v>
       </c>
-      <c r="H122" s="4">
+      <c r="H122" s="13">
         <v>634320</v>
       </c>
-      <c r="I122" s="5">
+      <c r="I122" s="14">
         <v>45965</v>
       </c>
-      <c r="J122" s="8">
+      <c r="J122" s="15">
         <v>1.4</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A123" s="7" t="s">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E123" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="12">
         <v>27</v>
       </c>
-      <c r="G123" s="4">
+      <c r="G123" s="13">
         <v>80578</v>
       </c>
-      <c r="H123" s="4">
+      <c r="H123" s="13">
         <v>2175606</v>
       </c>
-      <c r="I123" s="5">
+      <c r="I123" s="14">
         <v>45923</v>
       </c>
-      <c r="J123" s="8">
+      <c r="J123" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A124" s="7" t="s">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E124" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="12">
         <v>6</v>
       </c>
-      <c r="G124" s="4">
+      <c r="G124" s="13">
         <v>25356</v>
       </c>
-      <c r="H124" s="4">
+      <c r="H124" s="13">
         <v>152136</v>
       </c>
-      <c r="I124" s="5">
+      <c r="I124" s="14">
         <v>45940</v>
       </c>
-      <c r="J124" s="8">
+      <c r="J124" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A125" s="7" t="s">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="12">
         <v>46</v>
       </c>
-      <c r="G125" s="4">
+      <c r="G125" s="13">
         <v>8231</v>
       </c>
-      <c r="H125" s="4">
+      <c r="H125" s="13">
         <v>378626</v>
       </c>
-      <c r="I125" s="5">
+      <c r="I125" s="14">
         <v>45630</v>
       </c>
-      <c r="J125" s="8">
+      <c r="J125" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A126" s="7" t="s">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126" s="12">
         <v>14</v>
       </c>
-      <c r="G126" s="4">
+      <c r="G126" s="13">
         <v>56442</v>
       </c>
-      <c r="H126" s="4">
+      <c r="H126" s="13">
         <v>790188</v>
       </c>
-      <c r="I126" s="5">
+      <c r="I126" s="14">
         <v>45743</v>
       </c>
-      <c r="J126" s="8">
+      <c r="J126" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A127" s="7" t="s">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="12">
         <v>26</v>
       </c>
-      <c r="G127" s="4">
+      <c r="G127" s="13">
         <v>89346</v>
       </c>
-      <c r="H127" s="4">
+      <c r="H127" s="13">
         <v>2322996</v>
       </c>
-      <c r="I127" s="5">
+      <c r="I127" s="14">
         <v>45769</v>
       </c>
-      <c r="J127" s="8">
+      <c r="J127" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A128" s="7" t="s">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="E128" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="12">
         <v>6</v>
       </c>
-      <c r="G128" s="4">
+      <c r="G128" s="13">
         <v>31164</v>
       </c>
-      <c r="H128" s="4">
+      <c r="H128" s="13">
         <v>186984</v>
       </c>
-      <c r="I128" s="5">
+      <c r="I128" s="14">
         <v>45961</v>
       </c>
-      <c r="J128" s="8">
+      <c r="J128" s="15">
         <v>1.7</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A129" s="7" t="s">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="12">
         <v>32</v>
       </c>
-      <c r="G129" s="4">
+      <c r="G129" s="13">
         <v>39981</v>
       </c>
-      <c r="H129" s="4">
+      <c r="H129" s="13">
         <v>1279392</v>
       </c>
-      <c r="I129" s="5">
+      <c r="I129" s="14">
         <v>45832</v>
       </c>
-      <c r="J129" s="8">
+      <c r="J129" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A130" s="7" t="s">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130" s="12">
         <v>49</v>
       </c>
-      <c r="G130" s="4">
+      <c r="G130" s="13">
         <v>10424</v>
       </c>
-      <c r="H130" s="4">
+      <c r="H130" s="13">
         <v>510776</v>
       </c>
-      <c r="I130" s="5">
+      <c r="I130" s="14">
         <v>45817</v>
       </c>
-      <c r="J130" s="8">
+      <c r="J130" s="15">
         <v>4.8</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A131" s="7" t="s">
+      <c r="K130" s="6" cm="1">
+        <f t="array" aca="1" ref="K130" ca="1">K130:K151</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A131" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E131" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="12">
         <v>34</v>
       </c>
-      <c r="G131" s="4">
+      <c r="G131" s="13">
         <v>36206</v>
       </c>
-      <c r="H131" s="4">
+      <c r="H131" s="13">
         <v>1231004</v>
       </c>
-      <c r="I131" s="5">
+      <c r="I131" s="14">
         <v>45658</v>
       </c>
-      <c r="J131" s="8">
+      <c r="J131" s="15">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A132" s="7" t="s">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A132" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E132" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="12">
         <v>8</v>
       </c>
-      <c r="G132" s="4">
+      <c r="G132" s="13">
         <v>26595</v>
       </c>
-      <c r="H132" s="4">
+      <c r="H132" s="13">
         <v>212760</v>
       </c>
-      <c r="I132" s="5">
+      <c r="I132" s="14">
         <v>45627</v>
       </c>
-      <c r="J132" s="8">
+      <c r="J132" s="15">
         <v>4.3</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A133" s="7" t="s">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A133" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="12">
         <v>49</v>
       </c>
-      <c r="G133" s="4">
+      <c r="G133" s="13">
         <v>77216</v>
       </c>
-      <c r="H133" s="4">
+      <c r="H133" s="13">
         <v>3783584</v>
       </c>
-      <c r="I133" s="5">
+      <c r="I133" s="14">
         <v>45678</v>
       </c>
-      <c r="J133" s="8">
+      <c r="J133" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A134" s="7" t="s">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A134" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="E134" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="12">
         <v>6</v>
       </c>
-      <c r="G134" s="4">
+      <c r="G134" s="13">
         <v>65379</v>
       </c>
-      <c r="H134" s="4">
+      <c r="H134" s="13">
         <v>392274</v>
       </c>
-      <c r="I134" s="5">
+      <c r="I134" s="14">
         <v>45955</v>
       </c>
-      <c r="J134" s="8">
+      <c r="J134" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A135" s="7" t="s">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A135" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="E135" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="12">
         <v>35</v>
       </c>
-      <c r="G135" s="4">
+      <c r="G135" s="13">
         <v>6370</v>
       </c>
-      <c r="H135" s="4">
+      <c r="H135" s="13">
         <v>222950</v>
       </c>
-      <c r="I135" s="5">
+      <c r="I135" s="14">
         <v>45959</v>
       </c>
-      <c r="J135" s="8">
+      <c r="J135" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A136" s="7" t="s">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A136" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="12">
         <v>46</v>
       </c>
-      <c r="G136" s="4">
+      <c r="G136" s="13">
         <v>88601</v>
       </c>
-      <c r="H136" s="4">
+      <c r="H136" s="13">
         <v>4075646</v>
       </c>
-      <c r="I136" s="5">
+      <c r="I136" s="14">
         <v>45749</v>
       </c>
-      <c r="J136" s="8">
+      <c r="J136" s="15">
         <v>1.5</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A137" s="7" t="s">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A137" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E137" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="12">
         <v>22</v>
       </c>
-      <c r="G137" s="4">
+      <c r="G137" s="13">
         <v>86184</v>
       </c>
-      <c r="H137" s="4">
+      <c r="H137" s="13">
         <v>1896048</v>
       </c>
-      <c r="I137" s="5">
+      <c r="I137" s="14">
         <v>45968</v>
       </c>
-      <c r="J137" s="8">
+      <c r="J137" s="15">
         <v>1.8</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A138" s="7" t="s">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A138" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D138" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="12">
         <v>35</v>
       </c>
-      <c r="G138" s="4">
+      <c r="G138" s="13">
         <v>9569</v>
       </c>
-      <c r="H138" s="4">
+      <c r="H138" s="13">
         <v>334915</v>
       </c>
-      <c r="I138" s="5">
+      <c r="I138" s="14">
         <v>45861</v>
       </c>
-      <c r="J138" s="8">
+      <c r="J138" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A139" s="7" t="s">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D139" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E139" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139" s="12">
         <v>15</v>
       </c>
-      <c r="G139" s="4">
+      <c r="G139" s="13">
         <v>86332</v>
       </c>
-      <c r="H139" s="4">
+      <c r="H139" s="13">
         <v>1294980</v>
       </c>
-      <c r="I139" s="5">
+      <c r="I139" s="14">
         <v>45959</v>
       </c>
-      <c r="J139" s="8">
+      <c r="J139" s="15">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A140" s="7" t="s">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A140" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E140" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140" s="12">
         <v>30</v>
       </c>
-      <c r="G140" s="4">
+      <c r="G140" s="13">
         <v>13857</v>
       </c>
-      <c r="H140" s="4">
+      <c r="H140" s="13">
         <v>415710</v>
       </c>
-      <c r="I140" s="5">
+      <c r="I140" s="14">
         <v>45964</v>
       </c>
-      <c r="J140" s="8">
+      <c r="J140" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A141" s="7" t="s">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A141" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="D141" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E141" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141" s="12">
         <v>13</v>
       </c>
-      <c r="G141" s="4">
+      <c r="G141" s="13">
         <v>55120</v>
       </c>
-      <c r="H141" s="4">
+      <c r="H141" s="13">
         <v>716560</v>
       </c>
-      <c r="I141" s="5">
+      <c r="I141" s="14">
         <v>45708</v>
       </c>
-      <c r="J141" s="8">
+      <c r="J141" s="15">
         <v>2.1</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A142" s="7" t="s">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D142" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="E142" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="12">
         <v>37</v>
       </c>
-      <c r="G142" s="4">
+      <c r="G142" s="13">
         <v>21058</v>
       </c>
-      <c r="H142" s="4">
+      <c r="H142" s="13">
         <v>779146</v>
       </c>
-      <c r="I142" s="5">
+      <c r="I142" s="14">
         <v>45963</v>
       </c>
-      <c r="J142" s="8">
+      <c r="J142" s="15">
         <v>3.2</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A143" s="7" t="s">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A143" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D143" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="E143" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="12">
         <v>39</v>
       </c>
-      <c r="G143" s="4">
+      <c r="G143" s="13">
         <v>24579</v>
       </c>
-      <c r="H143" s="4">
+      <c r="H143" s="13">
         <v>958581</v>
       </c>
-      <c r="I143" s="5">
+      <c r="I143" s="14">
         <v>45702</v>
       </c>
-      <c r="J143" s="8">
+      <c r="J143" s="15">
         <v>4.3</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A144" s="7" t="s">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144" s="12">
         <v>34</v>
       </c>
-      <c r="G144" s="4">
+      <c r="G144" s="13">
         <v>29555</v>
       </c>
-      <c r="H144" s="4">
+      <c r="H144" s="13">
         <v>1004870</v>
       </c>
-      <c r="I144" s="5">
+      <c r="I144" s="14">
         <v>45666</v>
       </c>
-      <c r="J144" s="8">
+      <c r="J144" s="15">
         <v>1.5</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A145" s="7" t="s">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="E145" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145" s="12">
         <v>11</v>
       </c>
-      <c r="G145" s="4">
+      <c r="G145" s="13">
         <v>43336</v>
       </c>
-      <c r="H145" s="4">
+      <c r="H145" s="13">
         <v>476696</v>
       </c>
-      <c r="I145" s="5">
+      <c r="I145" s="14">
         <v>45675</v>
       </c>
-      <c r="J145" s="8">
+      <c r="J145" s="15">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A146" s="7" t="s">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E146" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="12">
         <v>7</v>
       </c>
-      <c r="G146" s="4">
+      <c r="G146" s="13">
         <v>27720</v>
       </c>
-      <c r="H146" s="4">
+      <c r="H146" s="13">
         <v>194040</v>
       </c>
-      <c r="I146" s="5">
+      <c r="I146" s="14">
         <v>45825</v>
       </c>
-      <c r="J146" s="8">
+      <c r="J146" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A147" s="7" t="s">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D147" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="12">
         <v>48</v>
       </c>
-      <c r="G147" s="4">
+      <c r="G147" s="13">
         <v>2569</v>
       </c>
-      <c r="H147" s="4">
+      <c r="H147" s="13">
         <v>123312</v>
       </c>
-      <c r="I147" s="5">
+      <c r="I147" s="14">
         <v>45668</v>
       </c>
-      <c r="J147" s="8">
+      <c r="J147" s="15">
         <v>1.3</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A148" s="7" t="s">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="E148" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="12">
         <v>10</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G148" s="13">
         <v>88281</v>
       </c>
-      <c r="H148" s="4">
+      <c r="H148" s="13">
         <v>882810</v>
       </c>
-      <c r="I148" s="5">
+      <c r="I148" s="14">
         <v>45869</v>
       </c>
-      <c r="J148" s="8">
+      <c r="J148" s="15">
         <v>3.9</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A149" s="7" t="s">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="E149" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149" s="12">
         <v>41</v>
       </c>
-      <c r="G149" s="4">
+      <c r="G149" s="13">
         <v>53121</v>
       </c>
-      <c r="H149" s="4">
+      <c r="H149" s="13">
         <v>2177961</v>
       </c>
-      <c r="I149" s="5">
+      <c r="I149" s="14">
         <v>45634</v>
       </c>
-      <c r="J149" s="8">
+      <c r="J149" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A150" s="7" t="s">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150" s="12">
         <v>49</v>
       </c>
-      <c r="G150" s="4">
+      <c r="G150" s="13">
         <v>83456</v>
       </c>
-      <c r="H150" s="4">
+      <c r="H150" s="13">
         <v>4089344</v>
       </c>
-      <c r="I150" s="5">
+      <c r="I150" s="14">
         <v>45634</v>
       </c>
-      <c r="J150" s="8">
+      <c r="J150" s="15">
         <v>4.7</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="19.2" x14ac:dyDescent="0.5">
-      <c r="A151" s="13" t="s">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B151" s="14" t="s">
+      <c r="B151" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C151" s="14" t="s">
+      <c r="C151" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D151" s="14" t="s">
+      <c r="D151" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="E151" s="14" t="s">
+      <c r="E151" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="F151" s="15">
+      <c r="F151" s="16">
         <v>38</v>
       </c>
-      <c r="G151" s="16">
+      <c r="G151" s="17">
         <v>19834</v>
       </c>
-      <c r="H151" s="16">
+      <c r="H151" s="17">
         <v>753692</v>
       </c>
-      <c r="I151" s="17">
+      <c r="I151" s="18">
         <v>45891</v>
       </c>
-      <c r="J151" s="18">
+      <c r="J151" s="19">
         <v>4.3</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="18" x14ac:dyDescent="0.5">
-      <c r="J152" s="1"/>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="22"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="22"/>
+      <c r="D152" s="22"/>
+      <c r="E152" s="22"/>
+      <c r="J152" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H155">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
-      <formula>75000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F164">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -6489,6 +6472,11 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H155">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+      <formula>75000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J151">
